--- a/examples/本地验收报告/政企部督办报告.xlsx
+++ b/examples/本地验收报告/政企部督办报告.xlsx
@@ -26,9 +26,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'风险分布'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'拖延原因'!$A$1:$B$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'部门完成情况'!$A$1:$B$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务清单'!$A$1:$AF$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'任务清单'!$A$1:$AF$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'重点任务'!$A$1:$AF$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'逾期任务'!$A$1:$AF$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'逾期任务'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'协办任务'!$A$1:$AF$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'责任人统计'!$A$1:$L$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'部门统计'!$A$1:$L$2</definedName>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1046,16 +1046,16 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -1065,13 +1065,13 @@
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>1</v>
@@ -1175,16 +1175,16 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>0</v>
@@ -1194,13 +1194,13 @@
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>1</v>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:08:08+08:00</t>
+          <t>2026-10-17T15:27:04+08:00</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1438,7 +1438,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -1515,11 +1515,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>尚未研判</t>
+          <t>资源依赖</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1575,7 +1575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1777,12 +1777,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>bc8d9a8e05ac470ab75fb9e03883bc54</t>
+          <t>4c502519187641b98e22f03d8158d84f</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>测试客户走访</t>
+          <t>测试原生政企部交付</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -1798,40 +1798,64 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>未开始</t>
+          <t>受阻</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>资源不足</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr"/>
       <c r="P2" s="2" t="inlineStr"/>
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:52.056054+08:00</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>邮件:SIM-NATIVE-1</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>资源不足</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>网络部</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:56+08:00</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="n">
@@ -1842,112 +1866,22 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:52+08:00</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:48+08:00</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>d1d4938f71884c7ca66786c9c0ab7e00</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>测试企业专线交付</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>政企部</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>受阻</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>两处资源不足</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:52+08:00</t>
-        </is>
-      </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
           <t>管理员</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr"/>
-      <c r="V3" s="2" t="inlineStr"/>
-      <c r="W3" s="2" t="inlineStr"/>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:52+08:00</t>
-        </is>
-      </c>
-      <c r="AE3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AF3" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AF3"/>
+  <autoFilter ref="A1:AF2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2160,12 +2094,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>d1d4938f71884c7ca66786c9c0ab7e00</t>
+          <t>4c502519187641b98e22f03d8158d84f</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>测试企业专线交付</t>
+          <t>测试原生政企部交付</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -2181,14 +2115,10 @@
       <c r="I2" s="2" t="inlineStr"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>受阻</t>
@@ -2197,7 +2127,7 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>两处资源不足</t>
+          <t>资源不足</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr"/>
@@ -2205,45 +2135,65 @@
       <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:52+08:00</t>
+          <t>2026-10-17T15:26:52.056054+08:00</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>管理员</t>
+          <t>邮件:SIM-NATIVE-1</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟：资源依赖待核实</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>资源不足</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>脚本化模拟建议：确认交付安排</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>网络部</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-17T15:26:56+08:00</t>
+        </is>
+      </c>
       <c r="Z2" s="2" t="inlineStr"/>
       <c r="AA2" s="2" t="inlineStr"/>
       <c r="AB2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:52+08:00</t>
+          <t>2026-10-17T15:26:52+08:00</t>
         </is>
       </c>
       <c r="AE2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-17T15:07:46+08:00</t>
+          <t>2026-10-17T15:26:48+08:00</t>
         </is>
       </c>
       <c r="AF2" s="2" t="inlineStr">
         <is>
-          <t>Excel导入</t>
+          <t>管理员</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2458,98 +2408,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>d1d4938f71884c7ca66786c9c0ab7e00</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>测试企业专线交付</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>政企部</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>受阻</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>两处资源不足</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:52+08:00</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>管理员</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>未研判</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:52+08:00</t>
-        </is>
-      </c>
-      <c r="AE2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-17T15:07:46+08:00</t>
-        </is>
-      </c>
-      <c r="AF2" s="2" t="inlineStr">
-        <is>
-          <t>Excel导入</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AF2"/>
+  <autoFilter ref="A1:AF1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
